--- a/sources/baek_step6.xlsx
+++ b/sources/baek_step6.xlsx
@@ -821,6 +821,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>a8cff31e-973f-4967-a9af-aeb862702e75</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>a8cff31e-973f-4967-a9af-aeb862702e75</t>
@@ -868,6 +873,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>23f4e603-2800-445d-a580-a5449bb4e6db</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>23f4e603-2800-445d-a580-a5449bb4e6db</t>
@@ -913,6 +923,11 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>c1e72722-088e-4713-997a-36ef818af837</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -6766,6 +6781,11 @@
           <t>hhlmmmhmlm</t>
         </is>
       </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>b9450184-4f85-4745-a77d-d804cc3878f8</t>
+        </is>
+      </c>
       <c r="Q118" t="inlineStr">
         <is>
           <t>b9450184-4f85-4745-a77d-d804cc3878f8</t>
@@ -6796,6 +6816,11 @@
       <c r="K119" t="inlineStr">
         <is>
           <t>hhhlmmmlm[!]</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>26c9b6a0-30d4-4ef8-b80e-04220b821fe5</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
